--- a/rlc_circuit_voltages_副本.xlsx
+++ b/rlc_circuit_voltages_副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Series RLC Circuit — Step Response (Underdamped)</t>
   </si>
@@ -87,20 +87,6 @@
   </si>
   <si>
     <t>V_C - Voltage across Capacitor (V)</t>
-  </si>
-  <si>
-    <r>
-      <t>嘿嘿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>iu</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -2982,7 +2968,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>920183018</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>6.41511579147151</c:v>
@@ -5536,8 +5522,8 @@
         <f t="shared" si="0"/>
         <v>1.83046998266207</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>20</v>
+      <c r="C23" s="10">
+        <v>920183018</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" si="2"/>
